--- a/kortdata/PL_Händelsekort.xlsx
+++ b/kortdata/PL_Händelsekort.xlsx
@@ -4926,7 +4926,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -5101,23 +5101,6 @@
       <c r="C10" t="inlineStr">
         <is>
           <t>' - ' mellan Fas och Kategori</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Hela filen</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Tomma kort</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Två platshållarkort ('- tom', utan text) trycktes sist i varje tryckfil — 2 × 4 = 8 blanka kort. Ej med på fliken Kort.</t>
         </is>
       </c>
     </row>
@@ -8701,7 +8684,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>54 unika × 4 exemplar = 216 tryckta kort, plus 2 tomma platshållarkort × 4 = 8 blanka kort</t>
+          <t>54 unika × 4 exemplar = 216 tryckta kort, plus 2 tomma platshållarkort × 4 = 8 blanka kort som trycktes av misstag och ska tas bort ur spelet (beslut K10). Ingår inte i kortdatan.</t>
         </is>
       </c>
     </row>
